--- a/simple_game_test/domain_df.xlsx
+++ b/simple_game_test/domain_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1952,6 +1952,546 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>91</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2025-04-08 00:02:38.371565</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>154</v>
+      </c>
+      <c r="D31" t="n">
+        <v>44</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>The game was very engaging</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>['1', '-1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>93</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-04-08 00:03:47.477463</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>156</v>
+      </c>
+      <c r="D32" t="n">
+        <v>44</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>['2', '-1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>95</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-04-08 00:20:14.816866</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>154</v>
+      </c>
+      <c r="D33" t="n">
+        <v>44</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" t="n">
+        <v>4</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>The study was engaging</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>['0', '-1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>96</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-04-08 00:20:52.355623</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>156</v>
+      </c>
+      <c r="D34" t="n">
+        <v>44</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" t="n">
+        <v>5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>['0', '2']</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>97</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-04-08 01:22:06.780121</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>161</v>
+      </c>
+      <c r="D35" t="n">
+        <v>46</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Waiting for my partner was particularly frustrating</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>['1', '1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>99</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-04-08 01:23:34.422313</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>160</v>
+      </c>
+      <c r="D36" t="n">
+        <v>46</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5</v>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>['3', '1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>101</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-04-08 01:24:51.442862</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>162</v>
+      </c>
+      <c r="D37" t="n">
+        <v>46</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>4</v>
+      </c>
+      <c r="J37" t="n">
+        <v>4</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>4</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>['0', '0']</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>103</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-04-08 01:26:34.873666</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>157</v>
+      </c>
+      <c r="D38" t="n">
+        <v>45</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4</v>
+      </c>
+      <c r="L38" t="n">
+        <v>4</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>['1', '-2']</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>105</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-04-08 01:43:41.220137</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>161</v>
+      </c>
+      <c r="D39" t="n">
+        <v>46</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3</v>
+      </c>
+      <c r="L39" t="n">
+        <v>4</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>['-1', '1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>106</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2025-04-08 01:44:04.478959</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>157</v>
+      </c>
+      <c r="D40" t="n">
+        <v>45</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>4</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>4</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>['1', '1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>107</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-04-08 01:45:44.445671</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>162</v>
+      </c>
+      <c r="D41" t="n">
+        <v>46</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4</v>
+      </c>
+      <c r="J41" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4</v>
+      </c>
+      <c r="L41" t="n">
+        <v>4</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>['1', '2']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/simple_game_test/domain_df.xlsx
+++ b/simple_game_test/domain_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2492,6 +2492,1386 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>108</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2025-04-08 03:02:29.203885</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>166</v>
+      </c>
+      <c r="D42" t="n">
+        <v>47</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>4</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>['-1', '1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>110</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2025-04-08 03:03:16.996905</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>163</v>
+      </c>
+      <c r="D43" t="n">
+        <v>47</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>4</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>im still slightly confused</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>['2', '1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>112</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2025-04-08 03:29:34.556322</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>166</v>
+      </c>
+      <c r="D44" t="n">
+        <v>47</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" t="n">
+        <v>5</v>
+      </c>
+      <c r="I44" t="n">
+        <v>4</v>
+      </c>
+      <c r="J44" t="n">
+        <v>4</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3</v>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>['1', '-1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>113</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2025-04-08 03:29:47.567562</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>163</v>
+      </c>
+      <c r="D45" t="n">
+        <v>47</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>5</v>
+      </c>
+      <c r="J45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>this was so confusing to me I feel kinda dumb lol</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>['1', '1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>114</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025-04-08 03:40:57.327046</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>170</v>
+      </c>
+      <c r="D46" t="n">
+        <v>49</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>4</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3</v>
+      </c>
+      <c r="L46" t="n">
+        <v>4</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>['3', '2']</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>116</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025-04-08 03:42:29.814148</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>168</v>
+      </c>
+      <c r="D47" t="n">
+        <v>49</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>4</v>
+      </c>
+      <c r="H47" t="n">
+        <v>5</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" t="n">
+        <v>4</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>enjoyable.</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>['-2', '3']</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>118</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025-04-09 14:37:39.248726</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>178</v>
+      </c>
+      <c r="D48" t="n">
+        <v>51</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>4</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" t="n">
+        <v>4</v>
+      </c>
+      <c r="J48" t="n">
+        <v>4</v>
+      </c>
+      <c r="K48" t="n">
+        <v>4</v>
+      </c>
+      <c r="L48" t="n">
+        <v>4</v>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>['-2', '2']</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025-04-09 14:38:37.922771</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>180</v>
+      </c>
+      <c r="D49" t="n">
+        <v>51</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4</v>
+      </c>
+      <c r="H49" t="n">
+        <v>5</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" t="n">
+        <v>5</v>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>['1', '1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>122</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-04-09 15:01:57.636089</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>178</v>
+      </c>
+      <c r="D50" t="n">
+        <v>51</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4</v>
+      </c>
+      <c r="I50" t="n">
+        <v>4</v>
+      </c>
+      <c r="J50" t="n">
+        <v>4</v>
+      </c>
+      <c r="K50" t="n">
+        <v>4</v>
+      </c>
+      <c r="L50" t="n">
+        <v>3</v>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>['1', '2']</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>123</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025-04-09 15:02:26.725722</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>180</v>
+      </c>
+      <c r="D51" t="n">
+        <v>51</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4</v>
+      </c>
+      <c r="H51" t="n">
+        <v>5</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2</v>
+      </c>
+      <c r="L51" t="n">
+        <v>2</v>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>['-1', '2']</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>124</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-04-09 15:43:48.768469</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>184</v>
+      </c>
+      <c r="D52" t="n">
+        <v>52</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>5</v>
+      </c>
+      <c r="I52" t="n">
+        <v>5</v>
+      </c>
+      <c r="J52" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" t="n">
+        <v>5</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2</v>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>['2', '0']</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-04-09 15:44:14.537094</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>182</v>
+      </c>
+      <c r="D53" t="n">
+        <v>52</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3</v>
+      </c>
+      <c r="L53" t="n">
+        <v>3</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>I would have liked more time with this game i enjoyed it though</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>['-1', '-2']</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-04-09 15:44:50.622733</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>185</v>
+      </c>
+      <c r="D54" t="n">
+        <v>52</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" t="n">
+        <v>5</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" t="n">
+        <v>4</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I needed a cheat sheet to look at for what gains and loses points. Also, the extra triangle confused me and I wasn't sure why it was there. </t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>['2', '3']</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-04-09 16:03:35.053610</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>184</v>
+      </c>
+      <c r="D55" t="n">
+        <v>52</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>5</v>
+      </c>
+      <c r="I55" t="n">
+        <v>4</v>
+      </c>
+      <c r="J55" t="n">
+        <v>4</v>
+      </c>
+      <c r="K55" t="n">
+        <v>5</v>
+      </c>
+      <c r="L55" t="n">
+        <v>3</v>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>['2', '1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-04-09 16:04:18.296283</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>182</v>
+      </c>
+      <c r="D56" t="n">
+        <v>52</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" t="n">
+        <v>4</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2</v>
+      </c>
+      <c r="L56" t="n">
+        <v>4</v>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>['-1', '1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025-04-09 16:04:49.266911</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>185</v>
+      </c>
+      <c r="D57" t="n">
+        <v>52</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>4</v>
+      </c>
+      <c r="H57" t="n">
+        <v>5</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2</v>
+      </c>
+      <c r="L57" t="n">
+        <v>5</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I was confused about moving through hexagon, but I figured it out fairly easily. </t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>['-1', '2']</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>133</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-04-09 16:23:11.039498</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>188</v>
+      </c>
+      <c r="D58" t="n">
+        <v>53</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>4</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4</v>
+      </c>
+      <c r="I58" t="n">
+        <v>4</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4</v>
+      </c>
+      <c r="L58" t="n">
+        <v>4</v>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>['-1', '2']</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025-04-09 16:39:16.231789</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>188</v>
+      </c>
+      <c r="D59" t="n">
+        <v>53</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>4</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4</v>
+      </c>
+      <c r="I59" t="n">
+        <v>4</v>
+      </c>
+      <c r="J59" t="n">
+        <v>4</v>
+      </c>
+      <c r="K59" t="n">
+        <v>4</v>
+      </c>
+      <c r="L59" t="n">
+        <v>2</v>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>['1', '1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>136</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025-04-09 16:42:28.634305</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>192</v>
+      </c>
+      <c r="D60" t="n">
+        <v>54</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>5</v>
+      </c>
+      <c r="G60" t="n">
+        <v>5</v>
+      </c>
+      <c r="H60" t="n">
+        <v>5</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>4</v>
+      </c>
+      <c r="L60" t="n">
+        <v>4</v>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>['3', '2']</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>138</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025-04-09 16:43:58.829917</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>186</v>
+      </c>
+      <c r="D61" t="n">
+        <v>54</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>4</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3</v>
+      </c>
+      <c r="H61" t="n">
+        <v>4</v>
+      </c>
+      <c r="I61" t="n">
+        <v>4</v>
+      </c>
+      <c r="J61" t="n">
+        <v>5</v>
+      </c>
+      <c r="K61" t="n">
+        <v>5</v>
+      </c>
+      <c r="L61" t="n">
+        <v>2</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>['-3', '3']</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>140</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025-04-09 17:00:34.051957</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>192</v>
+      </c>
+      <c r="D62" t="n">
+        <v>54</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>5</v>
+      </c>
+      <c r="H62" t="n">
+        <v>5</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="n">
+        <v>5</v>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>['-3', '4']</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>141</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025-04-09 17:11:43.978423</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>186</v>
+      </c>
+      <c r="D63" t="n">
+        <v>54</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>3</v>
+      </c>
+      <c r="G63" t="n">
+        <v>5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>4</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J63" t="n">
+        <v>4</v>
+      </c>
+      <c r="K63" t="n">
+        <v>5</v>
+      </c>
+      <c r="L63" t="n">
+        <v>4</v>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>['3', '1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>142</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025-04-09 17:12:26.075213</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>195</v>
+      </c>
+      <c r="D64" t="n">
+        <v>55</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>5</v>
+      </c>
+      <c r="G64" t="n">
+        <v>4</v>
+      </c>
+      <c r="H64" t="n">
+        <v>4</v>
+      </c>
+      <c r="I64" t="n">
+        <v>2</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2</v>
+      </c>
+      <c r="K64" t="n">
+        <v>4</v>
+      </c>
+      <c r="L64" t="n">
+        <v>4</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Having to wait over 15mins in the waiting room for the final participant was frustrating</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>['-2', '3']</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>143</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025-04-09 17:12:57.249521</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>194</v>
+      </c>
+      <c r="D65" t="n">
+        <v>55</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>4</v>
+      </c>
+      <c r="G65" t="n">
+        <v>4</v>
+      </c>
+      <c r="H65" t="n">
+        <v>5</v>
+      </c>
+      <c r="I65" t="n">
+        <v>2</v>
+      </c>
+      <c r="J65" t="n">
+        <v>4</v>
+      </c>
+      <c r="K65" t="n">
+        <v>2</v>
+      </c>
+      <c r="L65" t="n">
+        <v>4</v>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>['0', '-1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>145</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025-04-09 17:13:14.324446</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>193</v>
+      </c>
+      <c r="D66" t="n">
+        <v>55</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>4</v>
+      </c>
+      <c r="H66" t="n">
+        <v>4</v>
+      </c>
+      <c r="I66" t="n">
+        <v>4</v>
+      </c>
+      <c r="J66" t="n">
+        <v>4</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2</v>
+      </c>
+      <c r="L66" t="n">
+        <v>4</v>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>['-2', '1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>148</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025-04-09 17:41:47.154641</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>195</v>
+      </c>
+      <c r="D67" t="n">
+        <v>55</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>3</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J67" t="n">
+        <v>5</v>
+      </c>
+      <c r="K67" t="n">
+        <v>4</v>
+      </c>
+      <c r="L67" t="n">
+        <v>2</v>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>['3', '1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>149</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025-04-09 17:42:16.003179</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>194</v>
+      </c>
+      <c r="D68" t="n">
+        <v>55</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>4</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3</v>
+      </c>
+      <c r="I68" t="n">
+        <v>5</v>
+      </c>
+      <c r="J68" t="n">
+        <v>5</v>
+      </c>
+      <c r="K68" t="n">
+        <v>5</v>
+      </c>
+      <c r="L68" t="n">
+        <v>2</v>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>['0', '0']</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>150</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025-04-09 17:43:56.541098</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>193</v>
+      </c>
+      <c r="D69" t="n">
+        <v>55</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>5</v>
+      </c>
+      <c r="H69" t="n">
+        <v>5</v>
+      </c>
+      <c r="I69" t="n">
+        <v>2</v>
+      </c>
+      <c r="J69" t="n">
+        <v>5</v>
+      </c>
+      <c r="K69" t="n">
+        <v>4</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>I thought I would do well on Game 2 but it turns out I was mostly wrong.</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>['1', '2']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/simple_game_test/domain_df.xlsx
+++ b/simple_game_test/domain_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,11 +509,15 @@
           <t>2025-04-03 03:40:32.806141</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>91</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -557,11 +561,15 @@
           <t>2025-04-03 03:40:36.334275</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>89</v>
-      </c>
-      <c r="D3" t="n">
-        <v>24</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -605,11 +613,15 @@
           <t>2025-04-03 03:40:44.553316</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>90</v>
-      </c>
-      <c r="D4" t="n">
-        <v>24</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -653,11 +665,15 @@
           <t>2025-04-03 04:04:20.413111</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>91</v>
-      </c>
-      <c r="D5" t="n">
-        <v>24</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -701,11 +717,15 @@
           <t>2025-04-03 09:44:53.427964</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>99</v>
-      </c>
-      <c r="D6" t="n">
-        <v>27</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -749,11 +769,15 @@
           <t>2025-04-03 09:46:51.279058</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>98</v>
-      </c>
-      <c r="D7" t="n">
-        <v>27</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -801,11 +825,15 @@
           <t>2025-04-03 10:07:33.147193</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>99</v>
-      </c>
-      <c r="D8" t="n">
-        <v>27</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -849,11 +877,15 @@
           <t>2025-04-03 10:07:53.660146</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>98</v>
-      </c>
-      <c r="D9" t="n">
-        <v>27</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -897,11 +929,15 @@
           <t>2025-04-03 10:12:02.929742</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>101</v>
-      </c>
-      <c r="D10" t="n">
-        <v>28</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -945,11 +981,15 @@
           <t>2025-04-03 10:13:54.488612</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>103</v>
-      </c>
-      <c r="D11" t="n">
-        <v>28</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -997,11 +1037,15 @@
           <t>2025-04-03 10:14:31.266054</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>102</v>
-      </c>
-      <c r="D12" t="n">
-        <v>28</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1045,11 +1089,15 @@
           <t>2025-04-03 10:44:34.183810</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>101</v>
-      </c>
-      <c r="D13" t="n">
-        <v>28</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1093,11 +1141,15 @@
           <t>2025-04-03 10:44:46.423274</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>103</v>
-      </c>
-      <c r="D14" t="n">
-        <v>28</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1145,11 +1197,15 @@
           <t>2025-04-03 10:45:32.097249</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>102</v>
-      </c>
-      <c r="D15" t="n">
-        <v>28</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1193,11 +1249,15 @@
           <t>2025-04-03 11:36:21.847264</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>114</v>
-      </c>
-      <c r="D16" t="n">
-        <v>30</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1245,11 +1305,15 @@
           <t>2025-04-03 11:37:36.844186</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>110</v>
-      </c>
-      <c r="D17" t="n">
-        <v>30</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1297,11 +1361,15 @@
           <t>2025-04-03 11:48:08.696687</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>110</v>
-      </c>
-      <c r="D18" t="n">
-        <v>30</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1349,11 +1417,15 @@
           <t>2025-04-03 11:48:40.436299</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>114</v>
-      </c>
-      <c r="D19" t="n">
-        <v>30</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1401,11 +1473,15 @@
           <t>2025-04-03 11:57:14.077304</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>113</v>
-      </c>
-      <c r="D20" t="n">
-        <v>31</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1453,11 +1529,15 @@
           <t>2025-04-03 11:58:06.223749</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>107</v>
-      </c>
-      <c r="D21" t="n">
-        <v>31</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1505,11 +1585,15 @@
           <t>2025-04-03 12:02:02.578032</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>111</v>
-      </c>
-      <c r="D22" t="n">
-        <v>29</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1553,11 +1637,15 @@
           <t>2025-04-03 12:35:26.560978</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>113</v>
-      </c>
-      <c r="D23" t="n">
-        <v>31</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1605,11 +1693,15 @@
           <t>2025-04-03 12:35:28.523757</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>107</v>
-      </c>
-      <c r="D24" t="n">
-        <v>31</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1657,11 +1749,15 @@
           <t>2025-04-03 13:00:51.827918</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>112</v>
-      </c>
-      <c r="D25" t="n">
-        <v>32</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1705,11 +1801,15 @@
           <t>2025-04-03 13:05:42.201052</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>117</v>
-      </c>
-      <c r="D26" t="n">
-        <v>32</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1757,11 +1857,15 @@
           <t>2025-04-03 13:18:16.174849</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>118</v>
-      </c>
-      <c r="D27" t="n">
-        <v>33</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1809,11 +1913,15 @@
           <t>2025-04-03 13:21:01.471784</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>119</v>
-      </c>
-      <c r="D28" t="n">
-        <v>33</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1861,11 +1969,15 @@
           <t>2025-04-03 13:28:41.122160</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>117</v>
-      </c>
-      <c r="D29" t="n">
-        <v>32</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1913,11 +2025,15 @@
           <t>2025-04-03 13:28:49.487169</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>112</v>
-      </c>
-      <c r="D30" t="n">
-        <v>32</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1961,11 +2077,15 @@
           <t>2025-04-08 00:02:38.371565</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>154</v>
-      </c>
-      <c r="D31" t="n">
-        <v>44</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2013,11 +2133,15 @@
           <t>2025-04-08 00:03:47.477463</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>156</v>
-      </c>
-      <c r="D32" t="n">
-        <v>44</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2061,11 +2185,15 @@
           <t>2025-04-08 00:20:14.816866</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>154</v>
-      </c>
-      <c r="D33" t="n">
-        <v>44</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2113,11 +2241,15 @@
           <t>2025-04-08 00:20:52.355623</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>156</v>
-      </c>
-      <c r="D34" t="n">
-        <v>44</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2161,11 +2293,15 @@
           <t>2025-04-08 01:22:06.780121</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>161</v>
-      </c>
-      <c r="D35" t="n">
-        <v>46</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2213,11 +2349,15 @@
           <t>2025-04-08 01:23:34.422313</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>160</v>
-      </c>
-      <c r="D36" t="n">
-        <v>46</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2261,11 +2401,15 @@
           <t>2025-04-08 01:24:51.442862</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>162</v>
-      </c>
-      <c r="D37" t="n">
-        <v>46</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2309,11 +2453,15 @@
           <t>2025-04-08 01:26:34.873666</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>157</v>
-      </c>
-      <c r="D38" t="n">
-        <v>45</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2357,11 +2505,15 @@
           <t>2025-04-08 01:43:41.220137</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>161</v>
-      </c>
-      <c r="D39" t="n">
-        <v>46</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2405,11 +2557,15 @@
           <t>2025-04-08 01:44:04.478959</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>157</v>
-      </c>
-      <c r="D40" t="n">
-        <v>45</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2453,11 +2609,15 @@
           <t>2025-04-08 01:45:44.445671</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>162</v>
-      </c>
-      <c r="D41" t="n">
-        <v>46</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2501,11 +2661,15 @@
           <t>2025-04-08 03:02:29.203885</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v>166</v>
-      </c>
-      <c r="D42" t="n">
-        <v>47</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2549,11 +2713,15 @@
           <t>2025-04-08 03:03:16.996905</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v>163</v>
-      </c>
-      <c r="D43" t="n">
-        <v>47</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2601,11 +2769,15 @@
           <t>2025-04-08 03:29:34.556322</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>166</v>
-      </c>
-      <c r="D44" t="n">
-        <v>47</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2649,11 +2821,15 @@
           <t>2025-04-08 03:29:47.567562</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>163</v>
-      </c>
-      <c r="D45" t="n">
-        <v>47</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2701,11 +2877,15 @@
           <t>2025-04-08 03:40:57.327046</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>170</v>
-      </c>
-      <c r="D46" t="n">
-        <v>49</v>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2753,11 +2933,15 @@
           <t>2025-04-08 03:42:29.814148</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>168</v>
-      </c>
-      <c r="D47" t="n">
-        <v>49</v>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2805,11 +2989,15 @@
           <t>2025-04-09 14:37:39.248726</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>178</v>
-      </c>
-      <c r="D48" t="n">
-        <v>51</v>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2853,11 +3041,15 @@
           <t>2025-04-09 14:38:37.922771</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>180</v>
-      </c>
-      <c r="D49" t="n">
-        <v>51</v>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2901,11 +3093,15 @@
           <t>2025-04-09 15:01:57.636089</t>
         </is>
       </c>
-      <c r="C50" t="n">
-        <v>178</v>
-      </c>
-      <c r="D50" t="n">
-        <v>51</v>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2949,11 +3145,15 @@
           <t>2025-04-09 15:02:26.725722</t>
         </is>
       </c>
-      <c r="C51" t="n">
-        <v>180</v>
-      </c>
-      <c r="D51" t="n">
-        <v>51</v>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2997,11 +3197,15 @@
           <t>2025-04-09 15:43:48.768469</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v>184</v>
-      </c>
-      <c r="D52" t="n">
-        <v>52</v>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -3045,11 +3249,15 @@
           <t>2025-04-09 15:44:14.537094</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>182</v>
-      </c>
-      <c r="D53" t="n">
-        <v>52</v>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -3097,11 +3305,15 @@
           <t>2025-04-09 15:44:50.622733</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>185</v>
-      </c>
-      <c r="D54" t="n">
-        <v>52</v>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3149,11 +3361,15 @@
           <t>2025-04-09 16:03:35.053610</t>
         </is>
       </c>
-      <c r="C55" t="n">
-        <v>184</v>
-      </c>
-      <c r="D55" t="n">
-        <v>52</v>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3197,11 +3413,15 @@
           <t>2025-04-09 16:04:18.296283</t>
         </is>
       </c>
-      <c r="C56" t="n">
-        <v>182</v>
-      </c>
-      <c r="D56" t="n">
-        <v>52</v>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3245,11 +3465,15 @@
           <t>2025-04-09 16:04:49.266911</t>
         </is>
       </c>
-      <c r="C57" t="n">
-        <v>185</v>
-      </c>
-      <c r="D57" t="n">
-        <v>52</v>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3297,11 +3521,15 @@
           <t>2025-04-09 16:23:11.039498</t>
         </is>
       </c>
-      <c r="C58" t="n">
-        <v>188</v>
-      </c>
-      <c r="D58" t="n">
-        <v>53</v>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3345,11 +3573,15 @@
           <t>2025-04-09 16:39:16.231789</t>
         </is>
       </c>
-      <c r="C59" t="n">
-        <v>188</v>
-      </c>
-      <c r="D59" t="n">
-        <v>53</v>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3393,11 +3625,15 @@
           <t>2025-04-09 16:42:28.634305</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v>192</v>
-      </c>
-      <c r="D60" t="n">
-        <v>54</v>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3441,11 +3677,15 @@
           <t>2025-04-09 16:43:58.829917</t>
         </is>
       </c>
-      <c r="C61" t="n">
-        <v>186</v>
-      </c>
-      <c r="D61" t="n">
-        <v>54</v>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3489,11 +3729,15 @@
           <t>2025-04-09 17:00:34.051957</t>
         </is>
       </c>
-      <c r="C62" t="n">
-        <v>192</v>
-      </c>
-      <c r="D62" t="n">
-        <v>54</v>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -3537,11 +3781,15 @@
           <t>2025-04-09 17:11:43.978423</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>186</v>
-      </c>
-      <c r="D63" t="n">
-        <v>54</v>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -3585,11 +3833,15 @@
           <t>2025-04-09 17:12:26.075213</t>
         </is>
       </c>
-      <c r="C64" t="n">
-        <v>195</v>
-      </c>
-      <c r="D64" t="n">
-        <v>55</v>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3637,11 +3889,15 @@
           <t>2025-04-09 17:12:57.249521</t>
         </is>
       </c>
-      <c r="C65" t="n">
-        <v>194</v>
-      </c>
-      <c r="D65" t="n">
-        <v>55</v>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3685,11 +3941,15 @@
           <t>2025-04-09 17:13:14.324446</t>
         </is>
       </c>
-      <c r="C66" t="n">
-        <v>193</v>
-      </c>
-      <c r="D66" t="n">
-        <v>55</v>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3733,11 +3993,15 @@
           <t>2025-04-09 17:41:47.154641</t>
         </is>
       </c>
-      <c r="C67" t="n">
-        <v>195</v>
-      </c>
-      <c r="D67" t="n">
-        <v>55</v>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3781,11 +4045,15 @@
           <t>2025-04-09 17:42:16.003179</t>
         </is>
       </c>
-      <c r="C68" t="n">
-        <v>194</v>
-      </c>
-      <c r="D68" t="n">
-        <v>55</v>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3829,11 +4097,15 @@
           <t>2025-04-09 17:43:56.541098</t>
         </is>
       </c>
-      <c r="C69" t="n">
-        <v>193</v>
-      </c>
-      <c r="D69" t="n">
-        <v>55</v>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3869,6 +4141,430 @@
       <c r="N69" t="inlineStr">
         <is>
           <t>['1', '2']</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>151</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025-04-10 06:51:47.132625</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>5</v>
+      </c>
+      <c r="G70" t="n">
+        <v>4</v>
+      </c>
+      <c r="H70" t="n">
+        <v>5</v>
+      </c>
+      <c r="I70" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" t="n">
+        <v>4</v>
+      </c>
+      <c r="K70" t="n">
+        <v>4</v>
+      </c>
+      <c r="L70" t="n">
+        <v>3</v>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>['-3', '3']</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>153</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025-04-10 07:11:11.593444</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>5</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H71" t="n">
+        <v>5</v>
+      </c>
+      <c r="I71" t="n">
+        <v>2</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2</v>
+      </c>
+      <c r="K71" t="n">
+        <v>4</v>
+      </c>
+      <c r="L71" t="n">
+        <v>5</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>The more I practiced, the more I understood the game better and better.</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>['1', '1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>155</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025-04-10 07:14:57.906586</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2</v>
+      </c>
+      <c r="L72" t="n">
+        <v>5</v>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>['2', '6']</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>157</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025-04-10 07:15:38.370505</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>4</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4</v>
+      </c>
+      <c r="H73" t="n">
+        <v>5</v>
+      </c>
+      <c r="I73" t="n">
+        <v>4</v>
+      </c>
+      <c r="J73" t="n">
+        <v>4</v>
+      </c>
+      <c r="K73" t="n">
+        <v>4</v>
+      </c>
+      <c r="L73" t="n">
+        <v>4</v>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>['5', '10']</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>159</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025-04-10 07:19:10.284563</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>4</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4</v>
+      </c>
+      <c r="H74" t="n">
+        <v>4</v>
+      </c>
+      <c r="I74" t="n">
+        <v>4</v>
+      </c>
+      <c r="J74" t="n">
+        <v>5</v>
+      </c>
+      <c r="K74" t="n">
+        <v>4</v>
+      </c>
+      <c r="L74" t="n">
+        <v>3</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>As there was little or no interactiom with orange rectangle in the demonstration, hard to understand the the increase in power if you pick up - in the 2 tests</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>['1', '0']</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>161</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025-04-10 07:24:40.740097</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4</v>
+      </c>
+      <c r="H75" t="n">
+        <v>4</v>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2</v>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>['1', '4']</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>162</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025-04-10 07:44:21.372364</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G76" t="n">
+        <v>4</v>
+      </c>
+      <c r="H76" t="n">
+        <v>4</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>4</v>
+      </c>
+      <c r="K76" t="n">
+        <v>4</v>
+      </c>
+      <c r="L76" t="n">
+        <v>4</v>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>['10', '50']</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>163</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025-04-10 07:45:33.584790</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2</v>
+      </c>
+      <c r="H77" t="n">
+        <v>4</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="n">
+        <v>4</v>
+      </c>
+      <c r="L77" t="n">
+        <v>4</v>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>['4', '3']</t>
         </is>
       </c>
     </row>

--- a/simple_game_test/domain_df.xlsx
+++ b/simple_game_test/domain_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4568,6 +4568,754 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>169</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025-04-17 05:53:40.204343</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>5</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2</v>
+      </c>
+      <c r="H78" t="n">
+        <v>4</v>
+      </c>
+      <c r="I78" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>4</v>
+      </c>
+      <c r="K78" t="n">
+        <v>4</v>
+      </c>
+      <c r="L78" t="n">
+        <v>4</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>full engagement is key to learning the game</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>['3', '-3']</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>171</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025-04-17 05:57:54.921395</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>4</v>
+      </c>
+      <c r="G79" t="n">
+        <v>4</v>
+      </c>
+      <c r="H79" t="n">
+        <v>4</v>
+      </c>
+      <c r="I79" t="n">
+        <v>3</v>
+      </c>
+      <c r="J79" t="n">
+        <v>4</v>
+      </c>
+      <c r="K79" t="n">
+        <v>4</v>
+      </c>
+      <c r="L79" t="n">
+        <v>4</v>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>['3', '3']</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>173</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025-04-17 06:12:57.953592</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>4</v>
+      </c>
+      <c r="G80" t="n">
+        <v>3</v>
+      </c>
+      <c r="H80" t="n">
+        <v>4</v>
+      </c>
+      <c r="I80" t="n">
+        <v>4</v>
+      </c>
+      <c r="J80" t="n">
+        <v>4</v>
+      </c>
+      <c r="K80" t="n">
+        <v>3</v>
+      </c>
+      <c r="L80" t="n">
+        <v>3</v>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>['2', '3']</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>174</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025-04-17 06:13:09.173941</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>4</v>
+      </c>
+      <c r="G81" t="n">
+        <v>5</v>
+      </c>
+      <c r="H81" t="n">
+        <v>5</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2</v>
+      </c>
+      <c r="K81" t="n">
+        <v>5</v>
+      </c>
+      <c r="L81" t="n">
+        <v>4</v>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>['1', '0']</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>176</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025-04-17 06:13:23.940424</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>5</v>
+      </c>
+      <c r="G82" t="n">
+        <v>4</v>
+      </c>
+      <c r="H82" t="n">
+        <v>5</v>
+      </c>
+      <c r="I82" t="n">
+        <v>2</v>
+      </c>
+      <c r="J82" t="n">
+        <v>2</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" t="n">
+        <v>5</v>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>['1', '0']</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>179</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2025-04-17 06:19:14.928618</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>5</v>
+      </c>
+      <c r="G83" t="n">
+        <v>4</v>
+      </c>
+      <c r="H83" t="n">
+        <v>4</v>
+      </c>
+      <c r="I83" t="n">
+        <v>5</v>
+      </c>
+      <c r="J83" t="n">
+        <v>4</v>
+      </c>
+      <c r="K83" t="n">
+        <v>4</v>
+      </c>
+      <c r="L83" t="n">
+        <v>3</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>I still feel as if i have not understood the game fully</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>['2', '1']</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>181</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025-04-17 06:19:56.238686</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>4</v>
+      </c>
+      <c r="G84" t="n">
+        <v>4</v>
+      </c>
+      <c r="H84" t="n">
+        <v>4</v>
+      </c>
+      <c r="I84" t="n">
+        <v>3</v>
+      </c>
+      <c r="J84" t="n">
+        <v>3</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2</v>
+      </c>
+      <c r="L84" t="n">
+        <v>3</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>thanks was interesting to try and do</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>['3', '2']</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>183</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2025-04-17 06:22:10.920328</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>4</v>
+      </c>
+      <c r="H85" t="n">
+        <v>5</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>5</v>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>['-1', '0']</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>184</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2025-04-17 06:22:12.365756</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>3</v>
+      </c>
+      <c r="G86" t="n">
+        <v>4</v>
+      </c>
+      <c r="H86" t="n">
+        <v>4</v>
+      </c>
+      <c r="I86" t="n">
+        <v>2</v>
+      </c>
+      <c r="J86" t="n">
+        <v>2</v>
+      </c>
+      <c r="K86" t="n">
+        <v>5</v>
+      </c>
+      <c r="L86" t="n">
+        <v>5</v>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>['1', '3']</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>185</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2025-04-17 06:22:45.589356</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>4</v>
+      </c>
+      <c r="G87" t="n">
+        <v>4</v>
+      </c>
+      <c r="H87" t="n">
+        <v>3</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>2</v>
+      </c>
+      <c r="K87" t="n">
+        <v>2</v>
+      </c>
+      <c r="L87" t="n">
+        <v>4</v>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>['-3', '2']</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>186</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2025-04-17 06:42:09.173834</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>5</v>
+      </c>
+      <c r="G88" t="n">
+        <v>4</v>
+      </c>
+      <c r="H88" t="n">
+        <v>4</v>
+      </c>
+      <c r="I88" t="n">
+        <v>5</v>
+      </c>
+      <c r="J88" t="n">
+        <v>5</v>
+      </c>
+      <c r="K88" t="n">
+        <v>4</v>
+      </c>
+      <c r="L88" t="n">
+        <v>2</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>This game was also very confusing and inconsistant</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>['3', '2']</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>187</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2025-04-17 06:42:44.583536</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>4</v>
+      </c>
+      <c r="G89" t="n">
+        <v>5</v>
+      </c>
+      <c r="H89" t="n">
+        <v>3</v>
+      </c>
+      <c r="I89" t="n">
+        <v>3</v>
+      </c>
+      <c r="J89" t="n">
+        <v>3</v>
+      </c>
+      <c r="K89" t="n">
+        <v>3</v>
+      </c>
+      <c r="L89" t="n">
+        <v>3</v>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>['2', '3']</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>188</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2025-04-17 06:42:49.371276</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>4</v>
+      </c>
+      <c r="G90" t="n">
+        <v>4</v>
+      </c>
+      <c r="H90" t="n">
+        <v>4</v>
+      </c>
+      <c r="I90" t="n">
+        <v>4</v>
+      </c>
+      <c r="J90" t="n">
+        <v>4</v>
+      </c>
+      <c r="K90" t="n">
+        <v>4</v>
+      </c>
+      <c r="L90" t="n">
+        <v>4</v>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>['3', '3']</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>189</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2025-04-17 06:44:23.273206</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>5</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2</v>
+      </c>
+      <c r="H91" t="n">
+        <v>4</v>
+      </c>
+      <c r="I91" t="n">
+        <v>4</v>
+      </c>
+      <c r="J91" t="n">
+        <v>4</v>
+      </c>
+      <c r="K91" t="n">
+        <v>3</v>
+      </c>
+      <c r="L91" t="n">
+        <v>4</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>learning the game requires concentration</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>['-1', '3']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
